--- a/docs/verification/files/rocscience_gw/gw019.xlsx
+++ b/docs/verification/files/rocscience_gw/gw019.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="266">
   <si>
     <t>X</t>
   </si>
@@ -1023,6 +1023,9 @@
   </si>
   <si>
     <t>save_times</t>
+  </si>
+  <si>
+    <t>reservoir</t>
   </si>
 </sst>
 </file>
@@ -13710,7 +13713,7 @@
       <c r="C3" s="62"/>
       <c r="E3" s="32" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>reservoir</t>
         </is>
       </c>
       <c r="F3" s="33" t="inlineStr">
@@ -13835,7 +13838,9 @@
       <c r="O6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-      <c r="T6" s="1"/>
+      <c r="T6" s="1" t="s">
+        <v>265</v>
+      </c>
       <c r="U6" s="9"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
@@ -14101,7 +14106,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 H3 K3 N3 Q3" xr:uid="{21F200C9-4829-4345-9958-0F754F272AD0}">
-      <formula1>$T$4:$T$5</formula1>
+      <formula1>$T$4:$T$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14251,6 +14256,9 @@
       <c r="O6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
+      <c r="T6" s="1" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
@@ -14515,7 +14523,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 H3 K3 N3 Q3" xr:uid="{68C61D93-1721-F843-8E53-0F0E50006C65}">
-      <formula1>$T$4:$T$5</formula1>
+      <formula1>$T$4:$T$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/verification/files/rocscience_gw/gw019.xlsx
+++ b/docs/verification/files/rocscience_gw/gw019.xlsx
@@ -14256,9 +14256,6 @@
       <c r="O6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-      <c r="T6" s="1" t="s">
-        <v>265</v>
-      </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
@@ -14523,7 +14520,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 H3 K3 N3 Q3" xr:uid="{68C61D93-1721-F843-8E53-0F0E50006C65}">
-      <formula1>$T$4:$T$6</formula1>
+      <formula1>$T$4:$T$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15847,10 +15844,10 @@
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3">
-        <v>100000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N11" s="3">
-        <v>0.3</v>
+        <v>0.0</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -15977,10 +15974,10 @@
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3">
-        <v>100000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N12" s="3">
-        <v>0.3</v>
+        <v>0.0</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>

--- a/docs/verification/files/rocscience_gw/gw019.xlsx
+++ b/docs/verification/files/rocscience_gw/gw019.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8D9778-BA48-644C-980F-473DF9F954B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEB53F3-5E86-5B42-A7B6-55B20E1E8D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="310">
   <si>
     <t>time</t>
   </si>
@@ -971,7 +971,25 @@
     <t>corps</t>
   </si>
   <si>
-    <t>Mat ID = -1 --&gt; SSR reduce, Mat ID = -2 --&gt; SSR hold, Mat ID = -3 --&gt; SSR elastic</t>
+    <t>Size:</t>
+  </si>
+  <si>
+    <t>Direction:</t>
+  </si>
+  <si>
+    <t>material</t>
+  </si>
+  <si>
+    <t>Type: material zone (default), an SSR analysis overlay, or a mesh refinement region.   Size: optional target mesh element size inside the polygon (blank = global size).</t>
+  </si>
+  <si>
+    <t>Side BC:</t>
+  </si>
+  <si>
+    <t>rollers</t>
+  </si>
+  <si>
+    <t>Size: optional target mesh element size inside this line's material zone (blank = global size).</t>
   </si>
 </sst>
 </file>
@@ -1479,18 +1497,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="35">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1511,7 +1522,119 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1686,7 +1809,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$A$8:$A$27</c:f>
+              <c:f>profile!$A$9:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1695,7 +1818,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$B$8:$B$27</c:f>
+              <c:f>profile!$B$9:$B$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1749,7 +1872,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$D$8:$D$27</c:f>
+              <c:f>profile!$D$9:$D$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1758,7 +1881,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$E$8:$E$27</c:f>
+              <c:f>profile!$E$9:$E$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1812,7 +1935,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$G$8:$G$27</c:f>
+              <c:f>profile!$G$9:$G$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1821,7 +1944,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$H$8:$H$27</c:f>
+              <c:f>profile!$H$9:$H$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1875,7 +1998,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$J$8:$J$27</c:f>
+              <c:f>profile!$J$9:$J$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1884,7 +2007,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$K$8:$K$27</c:f>
+              <c:f>profile!$K$9:$K$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1938,7 +2061,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$M$8:$M$27</c:f>
+              <c:f>profile!$M$9:$M$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1947,7 +2070,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$N$8:$N$27</c:f>
+              <c:f>profile!$N$9:$N$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2001,7 +2124,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$P$8:$P$27</c:f>
+              <c:f>profile!$P$9:$P$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2010,7 +2133,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$Q$8:$Q$27</c:f>
+              <c:f>profile!$Q$9:$Q$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2070,7 +2193,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$S$8:$S$27</c:f>
+              <c:f>profile!$S$9:$S$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2079,7 +2202,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$T$8:$T$27</c:f>
+              <c:f>profile!$T$9:$T$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2139,7 +2262,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$V$8:$V$27</c:f>
+              <c:f>profile!$V$9:$V$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2148,7 +2271,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$W$8:$W$27</c:f>
+              <c:f>profile!$W$9:$W$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2208,7 +2331,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$Y$8:$Y$27</c:f>
+              <c:f>profile!$Y$9:$Y$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2217,7 +2340,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$Z$8:$Z$27</c:f>
+              <c:f>profile!$Z$9:$Z$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2277,7 +2400,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AB$8:$AB$27</c:f>
+              <c:f>profile!$AB$9:$AB$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2286,7 +2409,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AC$8:$AC$27</c:f>
+              <c:f>profile!$AC$9:$AC$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2346,7 +2469,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AE$8:$AE$27</c:f>
+              <c:f>profile!$AE$9:$AE$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2355,7 +2478,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AF$8:$AF$27</c:f>
+              <c:f>profile!$AF$9:$AF$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2415,7 +2538,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AH$8:$AH$27</c:f>
+              <c:f>profile!$AH$9:$AH$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2424,7 +2547,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AI$8:$AI$27</c:f>
+              <c:f>profile!$AI$9:$AI$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2484,7 +2607,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AK$8:$AK$27</c:f>
+              <c:f>profile!$AK$9:$AK$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2493,7 +2616,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AL$8:$AL$27</c:f>
+              <c:f>profile!$AL$9:$AL$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2556,7 +2679,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AN$8:$AN$27</c:f>
+              <c:f>profile!$AN$9:$AN$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2565,7 +2688,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AO$8:$AO$27</c:f>
+              <c:f>profile!$AO$9:$AO$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2628,7 +2751,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AQ$8:$AQ$27</c:f>
+              <c:f>profile!$AQ$9:$AQ$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2637,7 +2760,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AR$8:$AR$27</c:f>
+              <c:f>profile!$AR$9:$AR$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2879,7 +3002,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$B$4:$B$13</c:f>
+              <c:f>dloads!$B$5:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2888,7 +3011,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$C$4:$C$13</c:f>
+              <c:f>dloads!$C$5:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2951,7 +3074,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$F$4:$F$13</c:f>
+              <c:f>dloads!$F$5:$F$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2960,7 +3083,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$G$4:$G$13</c:f>
+              <c:f>dloads!$G$5:$G$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3023,7 +3146,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$J$4:$J$13</c:f>
+              <c:f>dloads!$J$5:$J$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3032,7 +3155,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$K$4:$K$13</c:f>
+              <c:f>dloads!$K$5:$K$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3095,7 +3218,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$N$4:$N$13</c:f>
+              <c:f>dloads!$N$5:$N$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3104,7 +3227,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$O$4:$O$13</c:f>
+              <c:f>dloads!$O$5:$O$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3167,7 +3290,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$R$4:$R$22</c:f>
+              <c:f>dloads!$R$5:$R$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3176,7 +3299,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$S$4:$S$22</c:f>
+              <c:f>dloads!$S$5:$S$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3239,7 +3362,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$V$4:$V$22</c:f>
+              <c:f>dloads!$V$5:$V$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3248,7 +3371,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$W$4:$W$22</c:f>
+              <c:f>dloads!$W$5:$W$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3496,7 +3619,7 @@
           </c:dPt>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$B$4:$B$22</c:f>
+              <c:f>'dloads (2)'!$B$5:$B$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3505,7 +3628,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$C$4:$C$22</c:f>
+              <c:f>'dloads (2)'!$C$5:$C$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3565,7 +3688,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$F$4:$F$22</c:f>
+              <c:f>'dloads (2)'!$F$5:$F$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3574,7 +3697,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$G$4:$G$22</c:f>
+              <c:f>'dloads (2)'!$G$5:$G$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3628,7 +3751,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$J$4:$J$22</c:f>
+              <c:f>'dloads (2)'!$J$5:$J$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3637,7 +3760,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$K$4:$K$22</c:f>
+              <c:f>'dloads (2)'!$K$5:$K$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3691,7 +3814,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$N$4:$N$22</c:f>
+              <c:f>'dloads (2)'!$N$5:$N$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3700,7 +3823,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$O$4:$O$22</c:f>
+              <c:f>'dloads (2)'!$O$5:$O$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3754,7 +3877,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$R$4:$R$22</c:f>
+              <c:f>'dloads (2)'!$R$5:$R$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3763,7 +3886,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$S$4:$S$22</c:f>
+              <c:f>'dloads (2)'!$S$5:$S$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3817,7 +3940,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$V$4:$V$22</c:f>
+              <c:f>'dloads (2)'!$V$5:$V$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3826,7 +3949,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$W$4:$W$22</c:f>
+              <c:f>'dloads (2)'!$W$5:$W$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -6241,7 +6364,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$A$8:$A$27</c:f>
+              <c:f>polygon!$A$10:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6250,7 +6373,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$B$8:$B$27</c:f>
+              <c:f>polygon!$B$10:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6310,7 +6433,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$D$8:$D$27</c:f>
+              <c:f>polygon!$D$10:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6319,7 +6442,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$E$8:$E$27</c:f>
+              <c:f>polygon!$E$10:$E$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6379,7 +6502,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$G$8:$G$27</c:f>
+              <c:f>polygon!$G$10:$G$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6388,7 +6511,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$H$8:$H$27</c:f>
+              <c:f>polygon!$H$10:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6448,7 +6571,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$J$8:$J$27</c:f>
+              <c:f>polygon!$J$10:$J$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6457,7 +6580,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$K$8:$K$27</c:f>
+              <c:f>polygon!$K$10:$K$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6520,7 +6643,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$M$8:$M$27</c:f>
+              <c:f>polygon!$M$10:$M$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6529,7 +6652,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$N$8:$N$27</c:f>
+              <c:f>polygon!$N$10:$N$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6592,7 +6715,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$P$8:$P$27</c:f>
+              <c:f>polygon!$P$10:$P$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6601,7 +6724,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$Q$8:$Q$27</c:f>
+              <c:f>polygon!$Q$10:$Q$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6664,7 +6787,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$S$8:$S$27</c:f>
+              <c:f>polygon!$S$10:$S$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6673,7 +6796,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$T$8:$T$27</c:f>
+              <c:f>polygon!$T$10:$T$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6736,7 +6859,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$V$8:$V$27</c:f>
+              <c:f>polygon!$V$10:$V$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6745,7 +6868,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$W$8:$W$27</c:f>
+              <c:f>polygon!$W$10:$W$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6808,7 +6931,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$Y$8:$Y$27</c:f>
+              <c:f>polygon!$Y$10:$Y$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6817,7 +6940,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$Z$8:$Z$27</c:f>
+              <c:f>polygon!$Z$10:$Z$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6880,7 +7003,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AB$8:$AB$27</c:f>
+              <c:f>polygon!$AB$10:$AB$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6889,7 +7012,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AC$8:$AC$27</c:f>
+              <c:f>polygon!$AC$10:$AC$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6949,7 +7072,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AE$8:$AE$27</c:f>
+              <c:f>polygon!$AE$10:$AE$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6958,7 +7081,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AF$8:$AF$27</c:f>
+              <c:f>polygon!$AF$10:$AF$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7018,7 +7141,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AH$8:$AH$27</c:f>
+              <c:f>polygon!$AH$10:$AH$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7027,7 +7150,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AI$8:$AI$27</c:f>
+              <c:f>polygon!$AI$10:$AI$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7087,7 +7210,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AK$8:$AK$27</c:f>
+              <c:f>polygon!$AK$10:$AK$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7096,7 +7219,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AL$8:$AL$27</c:f>
+              <c:f>polygon!$AL$10:$AL$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7156,7 +7279,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AN$8:$AN$27</c:f>
+              <c:f>polygon!$AN$10:$AN$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7165,7 +7288,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AO$8:$AO$27</c:f>
+              <c:f>polygon!$AO$10:$AO$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7225,7 +7348,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AQ$8:$AQ$27</c:f>
+              <c:f>polygon!$AQ$10:$AQ$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7234,7 +7357,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AR$8:$AR$27</c:f>
+              <c:f>polygon!$AR$10:$AR$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -8965,7 +9088,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="30">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9168,6 +9291,10 @@
       <c r="D21"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C22" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D22" s="1"/>
       <c r="F22" s="1" t="s">
         <v>62</v>
       </c>
@@ -9315,20 +9442,23 @@
   <mergeCells count="1">
     <mergeCell ref="B7:D7"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{4E2B12C7-FE67-3B4F-885D-33F99F4A0D82}">
+      <formula1>"rollers,fixed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{0D3EDF25-93C5-C944-8126-8CC9B17A21FC}">
       <formula1>$D$50:$D$51</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{4694A1A0-8B80-B646-8FBE-EF2E498B980D}">
       <formula1>$D$54:$D$57</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D17" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D17" xr:uid="{0356D3C6-ECF7-2D4C-8DB0-E3BFC9D663DB}">
       <formula1>$D$60:$D$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D14" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D14" xr:uid="{BDB1B4FF-9C3D-5F43-BB1B-429406E4C3E1}">
       <formula1>$D$64:$D$71</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{8A75E61B-C3DC-0F4A-869A-1DA1855E5B34}">
       <formula1>$D$74:$D$78</formula1>
     </dataValidation>
   </dataValidations>
@@ -9338,7 +9468,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="B2:X22"/>
+  <dimension ref="B2:X23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -9388,80 +9518,92 @@
       <c r="X2" s="62"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="39"/>
+      <c r="F3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="G3" s="58"/>
+      <c r="H3" s="39"/>
+      <c r="J3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="K3" s="58"/>
+      <c r="L3" s="39"/>
+      <c r="N3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="O3" s="58"/>
+      <c r="P3" s="39"/>
+      <c r="R3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="S3" s="58"/>
+      <c r="T3" s="39"/>
+      <c r="V3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="W3" s="58"/>
+      <c r="X3" s="39"/>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="3"/>
@@ -9823,15 +9965,46 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="V2:X2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="F2:H2"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="R3:S3"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 H3 L3 P3 T3 X3" xr:uid="{00000000-0002-0000-0900-000000000000}">
+      <formula1>"normal,vertical"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13361,20 +13534,20 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>vg</t>
+          <t>gard</t>
         </is>
       </c>
       <c r="AK11" s="3">
         <v>0.0</v>
       </c>
       <c r="AL11" s="3">
-        <v>0.0</v>
+        <v>-10.0</v>
       </c>
       <c r="AM11" s="3">
-        <v>0.1734</v>
+        <v>0.034372</v>
       </c>
       <c r="AN11" s="3">
-        <v>1.9124</v>
+        <v>3.45943</v>
       </c>
       <c r="AO11" s="3">
         <v>0.02</v>
@@ -13491,20 +13664,20 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>vg</t>
+          <t>gard</t>
         </is>
       </c>
       <c r="AK12" s="3">
         <v>0.0</v>
       </c>
       <c r="AL12" s="3">
-        <v>0.0</v>
+        <v>-10.0</v>
       </c>
       <c r="AM12" s="18">
-        <v>0.1734</v>
+        <v>0.034372</v>
       </c>
       <c r="AN12" s="19">
-        <v>1.9124</v>
+        <v>3.45943</v>
       </c>
       <c r="AO12" s="19">
         <v>0.02</v>
@@ -14776,84 +14949,84 @@
     <mergeCell ref="AG9:AP9"/>
   </mergeCells>
   <conditionalFormatting sqref="F11:K52 AB11:AF52">
-    <cfRule type="expression" dxfId="19" priority="6">
+    <cfRule type="expression" dxfId="34" priority="6">
       <formula>$E11="hb"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="7">
+    <cfRule type="expression" dxfId="33" priority="7">
       <formula>$E11="pow"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:L52 O11:R52">
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="32" priority="19">
       <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:G52">
-    <cfRule type="expression" dxfId="16" priority="8">
+    <cfRule type="expression" dxfId="31" priority="8">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:I52">
-    <cfRule type="expression" dxfId="15" priority="9">
+    <cfRule type="expression" dxfId="30" priority="9">
       <formula>$E11="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:K52">
-    <cfRule type="expression" dxfId="14" priority="10">
+    <cfRule type="expression" dxfId="29" priority="10">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P11:P52">
-    <cfRule type="expression" dxfId="13" priority="13">
+    <cfRule type="expression" dxfId="28" priority="13">
       <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"ru")</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q11:R52">
+    <cfRule type="expression" dxfId="27" priority="23">
+      <formula>$E11="cp"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="24">
+      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"piezo",$O11&lt;&gt;"seep")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="S11:V52">
-    <cfRule type="expression" dxfId="12" priority="11">
+    <cfRule type="expression" dxfId="25" priority="11">
       <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"pow")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W11:Z52">
-    <cfRule type="expression" dxfId="11" priority="12">
+    <cfRule type="expression" dxfId="24" priority="12">
       <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"hb")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB11:AF52">
-    <cfRule type="expression" dxfId="10" priority="21">
+    <cfRule type="expression" dxfId="23" priority="21">
       <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC11:AC52">
-    <cfRule type="expression" dxfId="9" priority="14">
+    <cfRule type="expression" dxfId="22" priority="14">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD11:AD52">
-    <cfRule type="expression" dxfId="8" priority="15">
+    <cfRule type="expression" dxfId="21" priority="15">
       <formula>$E11="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE11:AF52">
-    <cfRule type="expression" dxfId="7" priority="16">
+    <cfRule type="expression" dxfId="20" priority="16">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK11:AL52">
-    <cfRule type="expression" dxfId="6" priority="17">
+    <cfRule type="expression" dxfId="19" priority="17">
       <formula>OR($AJ11="vg",$AJ11="gard")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM11:AN52">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>$AJ11="lf"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:R52">
-    <cfRule type="expression" dxfId="1" priority="23">
-      <formula>$E11="cp"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="24">
-      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"piezo",$O11&lt;&gt;"seep")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -14873,7 +15046,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A2:AR27"/>
+  <dimension ref="A2:AR28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="1" customWidth="1"/>
@@ -14907,6 +15080,9 @@
       <c r="D2" s="24" t="s">
         <v>160</v>
       </c>
+      <c r="N2" s="24" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
@@ -15164,144 +15340,174 @@
       <c r="AR6" s="57"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="B7" s="37"/>
+      <c r="D7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" s="37"/>
+      <c r="G7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="H7" s="37"/>
+      <c r="J7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="K7" s="37"/>
+      <c r="M7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="N7" s="37"/>
+      <c r="P7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="T7" s="37"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="W7" s="37"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="Z7" s="37"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC7" s="37"/>
+      <c r="AE7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AF7" s="37"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AI7" s="37"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AL7" s="37"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO7" s="37"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AR7" s="37"/>
+    </row>
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="R7" s="1"/>
-      <c r="S7" s="2" t="s">
+      <c r="R8" s="1"/>
+      <c r="S8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="U7" s="1"/>
-      <c r="V7" s="2" t="s">
+      <c r="U8" s="1"/>
+      <c r="V8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="2" t="s">
+      <c r="X8" s="1"/>
+      <c r="Y8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="2" t="s">
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AC8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AE8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AF7" s="2" t="s">
+      <c r="AF8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AG7" s="1"/>
-      <c r="AH7" s="2" t="s">
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AI8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AJ7" s="1"/>
-      <c r="AK7" s="2" t="s">
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AL8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AM7" s="1"/>
-      <c r="AN7" s="2" t="s">
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AO7" s="2" t="s">
+      <c r="AO8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AP7" s="1"/>
-      <c r="AQ7" s="2" t="s">
+      <c r="AP8" s="1"/>
+      <c r="AQ8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AR7" s="2" t="s">
+      <c r="AR8" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="16"/>
-      <c r="AC8" s="17"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
-      <c r="AG8" s="1"/>
-      <c r="AH8" s="16"/>
-      <c r="AI8" s="17"/>
-      <c r="AJ8" s="1"/>
-      <c r="AK8" s="16"/>
-      <c r="AL8" s="17"/>
-      <c r="AM8" s="1"/>
-      <c r="AN8" s="16"/>
-      <c r="AO8" s="17"/>
-      <c r="AP8" s="1"/>
-      <c r="AQ8" s="16"/>
-      <c r="AR8" s="17"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
@@ -15317,31 +15523,31 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="1"/>
-      <c r="S9" s="18"/>
-      <c r="T9" s="19"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="17"/>
       <c r="U9" s="1"/>
-      <c r="V9" s="18"/>
-      <c r="W9" s="19"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="17"/>
       <c r="X9" s="1"/>
-      <c r="Y9" s="18"/>
-      <c r="Z9" s="19"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="17"/>
       <c r="AA9" s="1"/>
-      <c r="AB9" s="18"/>
-      <c r="AC9" s="19"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="17"/>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
       <c r="AG9" s="1"/>
-      <c r="AH9" s="18"/>
-      <c r="AI9" s="19"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="17"/>
       <c r="AJ9" s="1"/>
-      <c r="AK9" s="18"/>
-      <c r="AL9" s="19"/>
+      <c r="AK9" s="16"/>
+      <c r="AL9" s="17"/>
       <c r="AM9" s="1"/>
-      <c r="AN9" s="18"/>
-      <c r="AO9" s="19"/>
+      <c r="AN9" s="16"/>
+      <c r="AO9" s="17"/>
       <c r="AP9" s="1"/>
-      <c r="AQ9" s="18"/>
-      <c r="AR9" s="19"/>
+      <c r="AQ9" s="16"/>
+      <c r="AR9" s="17"/>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
@@ -15400,8 +15606,8 @@
       <c r="S11" s="18"/>
       <c r="T11" s="19"/>
       <c r="U11" s="1"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="17"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="19"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="18"/>
       <c r="Z11" s="19"/>
@@ -15437,31 +15643,31 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="1"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="19"/>
       <c r="U12" s="1"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="17"/>
       <c r="X12" s="1"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
+      <c r="Y12" s="18"/>
+      <c r="Z12" s="19"/>
       <c r="AA12" s="1"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="3"/>
+      <c r="AB12" s="18"/>
+      <c r="AC12" s="19"/>
       <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
       <c r="AG12" s="1"/>
-      <c r="AH12" s="3"/>
-      <c r="AI12" s="3"/>
+      <c r="AH12" s="18"/>
+      <c r="AI12" s="19"/>
       <c r="AJ12" s="1"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="3"/>
+      <c r="AK12" s="18"/>
+      <c r="AL12" s="19"/>
       <c r="AM12" s="1"/>
-      <c r="AN12" s="3"/>
-      <c r="AO12" s="3"/>
+      <c r="AN12" s="18"/>
+      <c r="AO12" s="19"/>
       <c r="AP12" s="1"/>
-      <c r="AQ12" s="3"/>
-      <c r="AR12" s="3"/>
+      <c r="AQ12" s="18"/>
+      <c r="AR12" s="19"/>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A13" s="3"/>
@@ -16063,6 +16269,46 @@
       <c r="AQ27" s="3"/>
       <c r="AR27" s="3"/>
     </row>
+    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="3"/>
+      <c r="AL28" s="3"/>
+      <c r="AM28" s="1"/>
+      <c r="AN28" s="3"/>
+      <c r="AO28" s="3"/>
+      <c r="AP28" s="1"/>
+      <c r="AQ28" s="3"/>
+      <c r="AR28" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="D4:E4"/>
@@ -16102,7 +16348,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A2:AR27"/>
+  <dimension ref="A2:AR29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="1" customWidth="1"/>
@@ -16131,7 +16377,7 @@
         <v>179</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -16210,397 +16456,475 @@
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="B5" s="39">
-        <v>1</v>
+        <v>198</v>
+      </c>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
       </c>
       <c r="D5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="E5" s="39">
-        <v>2</v>
+        <v>198</v>
+      </c>
+      <c r="E5" s="39" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
       </c>
       <c r="G5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="H5" s="39">
-        <v>3</v>
+        <v>198</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="K5" s="39">
-        <v>4</v>
+        <v>198</v>
+      </c>
+      <c r="K5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="M5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="N5" s="39">
-        <v>5</v>
+        <v>198</v>
+      </c>
+      <c r="N5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q5" s="39">
-        <v>6</v>
+        <v>198</v>
+      </c>
+      <c r="Q5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="T5" s="39">
-        <v>7</v>
+        <v>198</v>
+      </c>
+      <c r="T5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="W5" s="39">
-        <v>8</v>
+        <v>198</v>
+      </c>
+      <c r="W5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z5" s="39">
-        <v>9</v>
+        <v>198</v>
+      </c>
+      <c r="Z5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AC5" s="39">
-        <v>10</v>
+        <v>198</v>
+      </c>
+      <c r="AC5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="AE5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF5" s="39">
-        <v>11</v>
+        <v>198</v>
+      </c>
+      <c r="AF5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AI5" s="39">
-        <v>12</v>
+        <v>198</v>
+      </c>
+      <c r="AI5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AL5" s="39">
-        <v>13</v>
+        <v>198</v>
+      </c>
+      <c r="AL5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AO5" s="39">
-        <v>14</v>
+        <v>198</v>
+      </c>
+      <c r="AO5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR5" s="39" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A6" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="AR5" s="39">
+      <c r="B6" s="39">
+        <v>1</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="39">
+        <v>2</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="H6" s="39">
+        <v>3</v>
+      </c>
+      <c r="J6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="K6" s="39">
+        <v>4</v>
+      </c>
+      <c r="M6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="N6" s="39">
+        <v>5</v>
+      </c>
+      <c r="P6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q6" s="39">
+        <v>6</v>
+      </c>
+      <c r="R6" s="1"/>
+      <c r="S6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="T6" s="39">
+        <v>7</v>
+      </c>
+      <c r="U6" s="1"/>
+      <c r="V6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="W6" s="39">
+        <v>8</v>
+      </c>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z6" s="39">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AC6" s="39">
+        <v>10</v>
+      </c>
+      <c r="AE6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF6" s="39">
+        <v>11</v>
+      </c>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AI6" s="39">
+        <v>12</v>
+      </c>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL6" s="39">
+        <v>13</v>
+      </c>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AO6" s="39">
+        <v>14</v>
+      </c>
+      <c r="AP6" s="1"/>
+      <c r="AQ6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AR6" s="39">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="58" t="str">
-        <f>IF(B5=-1,"SSR reduce",IF(B5=-2,"SSR hold",IF(B5=-3,"SSR elastic",_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A7" s="58" t="str">
+        <f>IF(OR(B5="",B5="material"),_xlfn.XLOOKUP(B6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="B6" s="57"/>
-      <c r="D6" s="58" t="str">
-        <f>IF(E5=-1,"SSR reduce",IF(E5=-2,"SSR hold",IF(E5=-3,"SSR elastic",_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="B7" s="57"/>
+      <c r="D7" s="58" t="str">
+        <f>IF(OR(E5="",E5="material"),_xlfn.XLOOKUP(E6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="E6" s="57"/>
-      <c r="G6" s="58" t="str">
-        <f>IF(H5=-1,"SSR reduce",IF(H5=-2,"SSR hold",IF(H5=-3,"SSR elastic",_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="E7" s="57"/>
+      <c r="G7" s="58" t="str">
+        <f>IF(OR(H5="",H5="material"),_xlfn.XLOOKUP(H6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="H6" s="57"/>
-      <c r="J6" s="58" t="str">
-        <f>IF(K5=-1,"SSR reduce",IF(K5=-2,"SSR hold",IF(K5=-3,"SSR elastic",_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="H7" s="57"/>
+      <c r="J7" s="58" t="str">
+        <f>IF(OR(K5="",K5="material"),_xlfn.XLOOKUP(K6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="K6" s="57"/>
-      <c r="M6" s="58" t="str">
-        <f>IF(N5=-1,"SSR reduce",IF(N5=-2,"SSR hold",IF(N5=-3,"SSR elastic",_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="K7" s="57"/>
+      <c r="M7" s="58" t="str">
+        <f>IF(OR(N5="",N5="material"),_xlfn.XLOOKUP(N6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="N6" s="57"/>
-      <c r="P6" s="58" t="str">
-        <f>IF(Q5=-1,"SSR reduce",IF(Q5=-2,"SSR hold",IF(Q5=-3,"SSR elastic",_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="N7" s="57"/>
+      <c r="P7" s="58" t="str">
+        <f>IF(OR(Q5="",Q5="material"),_xlfn.XLOOKUP(Q6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="58" t="str">
-        <f>IF(T5=-1,"SSR reduce",IF(T5=-2,"SSR hold",IF(T5=-3,"SSR elastic",_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="Q7" s="57"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="58" t="str">
+        <f>IF(OR(T5="",T5="material"),_xlfn.XLOOKUP(T6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="T6" s="57"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="58" t="str">
-        <f>IF(W5=-1,"SSR reduce",IF(W5=-2,"SSR hold",IF(W5=-3,"SSR elastic",_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="T7" s="57"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="58" t="str">
+        <f>IF(OR(W5="",W5="material"),_xlfn.XLOOKUP(W6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="W6" s="57"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="58" t="str">
-        <f>IF(Z5=-1,"SSR reduce",IF(Z5=-2,"SSR hold",IF(Z5=-3,"SSR elastic",_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="W7" s="57"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="58" t="str">
+        <f>IF(OR(Z5="",Z5="material"),_xlfn.XLOOKUP(Z6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="Z6" s="57"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="58" t="str">
-        <f>IF(AC5=-1,"SSR reduce",IF(AC5=-2,"SSR hold",IF(AC5=-3,"SSR elastic",_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="Z7" s="57"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="58" t="str">
+        <f>IF(OR(AC5="",AC5="material"),_xlfn.XLOOKUP(AC6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="AC6" s="57"/>
-      <c r="AE6" s="58" t="str">
-        <f>IF(AF5=-1,"SSR reduce",IF(AF5=-2,"SSR hold",IF(AF5=-3,"SSR elastic",_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="AC7" s="57"/>
+      <c r="AE7" s="58" t="str">
+        <f>IF(OR(AF5="",AF5="material"),_xlfn.XLOOKUP(AF6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="AF6" s="57"/>
-      <c r="AG6" s="1"/>
-      <c r="AH6" s="58" t="str">
-        <f>IF(AI5=-1,"SSR reduce",IF(AI5=-2,"SSR hold",IF(AI5=-3,"SSR elastic",_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="AF7" s="57"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="58" t="str">
+        <f>IF(OR(AI5="",AI5="material"),_xlfn.XLOOKUP(AI6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="AI6" s="57"/>
-      <c r="AJ6" s="1"/>
-      <c r="AK6" s="58" t="str">
-        <f>IF(AL5=-1,"SSR reduce",IF(AL5=-2,"SSR hold",IF(AL5=-3,"SSR elastic",_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="AI7" s="57"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="58" t="str">
+        <f>IF(OR(AL5="",AL5="material"),_xlfn.XLOOKUP(AL6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="AL6" s="57"/>
-      <c r="AM6" s="1"/>
-      <c r="AN6" s="58" t="str">
-        <f>IF(AO5=-1,"SSR reduce",IF(AO5=-2,"SSR hold",IF(AO5=-3,"SSR elastic",_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="AL7" s="57"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="58" t="str">
+        <f>IF(OR(AO5="",AO5="material"),_xlfn.XLOOKUP(AO6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="AO6" s="57"/>
-      <c r="AP6" s="1"/>
-      <c r="AQ6" s="58" t="str">
-        <f>IF(AR5=-1,"SSR reduce",IF(AR5=-2,"SSR hold",IF(AR5=-3,"SSR elastic",_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="AO7" s="57"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="58" t="str">
+        <f>IF(OR(AR5="",AR5="material"),_xlfn.XLOOKUP(AR6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="AR6" s="57"/>
-    </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="AR7" s="57"/>
+    </row>
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="D8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="E8" s="39"/>
+      <c r="G8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="H8" s="39"/>
+      <c r="J8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="K8" s="39"/>
+      <c r="M8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="N8" s="39"/>
+      <c r="P8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="T8" s="39"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="W8" s="39"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="Z8" s="39"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC8" s="39"/>
+      <c r="AE8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AF8" s="39"/>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AI8" s="39"/>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AL8" s="39"/>
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO8" s="39"/>
+      <c r="AP8" s="1"/>
+      <c r="AQ8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AR8" s="39"/>
+    </row>
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="R7" s="1"/>
-      <c r="S7" s="2" t="s">
+      <c r="R9" s="1"/>
+      <c r="S9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="U7" s="1"/>
-      <c r="V7" s="2" t="s">
+      <c r="U9" s="1"/>
+      <c r="V9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="W9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="2" t="s">
+      <c r="X9" s="1"/>
+      <c r="Y9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="Z9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="2" t="s">
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AC9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AE9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AF7" s="2" t="s">
+      <c r="AF9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AG7" s="1"/>
-      <c r="AH7" s="2" t="s">
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AI9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AJ7" s="1"/>
-      <c r="AK7" s="2" t="s">
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AL9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AM7" s="1"/>
-      <c r="AN7" s="2" t="s">
+      <c r="AM9" s="1"/>
+      <c r="AN9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AO7" s="2" t="s">
+      <c r="AO9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AP7" s="1"/>
-      <c r="AQ7" s="2" t="s">
+      <c r="AP9" s="1"/>
+      <c r="AQ9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AR7" s="2" t="s">
+      <c r="AR9" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
-      <c r="AG8" s="1"/>
-      <c r="AH8" s="3"/>
-      <c r="AI8" s="3"/>
-      <c r="AJ8" s="1"/>
-      <c r="AK8" s="3"/>
-      <c r="AL8" s="3"/>
-      <c r="AM8" s="1"/>
-      <c r="AN8" s="3"/>
-      <c r="AO8" s="3"/>
-      <c r="AP8" s="1"/>
-      <c r="AQ8" s="3"/>
-      <c r="AR8" s="3"/>
-    </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>19.0</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D9" s="3">
-        <v>19.0</v>
-      </c>
-      <c r="E9" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="3"/>
-      <c r="AG9" s="1"/>
-      <c r="AH9" s="3"/>
-      <c r="AI9" s="3"/>
-      <c r="AJ9" s="1"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="3"/>
-      <c r="AM9" s="1"/>
-      <c r="AN9" s="3"/>
-      <c r="AO9" s="3"/>
-      <c r="AP9" s="1"/>
-      <c r="AQ9" s="3"/>
-      <c r="AR9" s="3"/>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
       <c r="B10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="3">
         <v>9.0</v>
-      </c>
-      <c r="D10" s="3">
-        <v>19.0</v>
-      </c>
-      <c r="E10" s="3">
-        <v>10.0</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -16639,16 +16963,16 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
+        <v>19.0</v>
+      </c>
+      <c r="B11" s="3">
         <v>0.0</v>
       </c>
-      <c r="B11" s="3">
+      <c r="D11" s="3">
+        <v>19.0</v>
+      </c>
+      <c r="E11" s="3">
         <v>9.0</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E11" s="3">
-        <v>10.0</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -16686,10 +17010,18 @@
       <c r="AR11" s="3"/>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="A12" s="3">
+        <v>19.0</v>
+      </c>
+      <c r="B12" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>19.0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>10.0</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="3"/>
@@ -16726,10 +17058,18 @@
       <c r="AR12" s="3"/>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="A13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="B13" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>10.0</v>
+      </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="J13" s="3"/>
@@ -17325,39 +17665,199 @@
       <c r="AQ27" s="3"/>
       <c r="AR27" s="3"/>
     </row>
+    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="3"/>
+      <c r="AL28" s="3"/>
+      <c r="AM28" s="1"/>
+      <c r="AN28" s="3"/>
+      <c r="AO28" s="3"/>
+      <c r="AP28" s="1"/>
+      <c r="AQ28" s="3"/>
+      <c r="AR28" s="3"/>
+    </row>
+    <row r="29" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="3"/>
+      <c r="AC29" s="3"/>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="1"/>
+      <c r="AH29" s="3"/>
+      <c r="AI29" s="3"/>
+      <c r="AJ29" s="1"/>
+      <c r="AK29" s="3"/>
+      <c r="AL29" s="3"/>
+      <c r="AM29" s="1"/>
+      <c r="AN29" s="3"/>
+      <c r="AO29" s="3"/>
+      <c r="AP29" s="1"/>
+      <c r="AQ29" s="3"/>
+      <c r="AR29" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="AN7:AO7"/>
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="Y7:Z7"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="AK7:AL7"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="P7:Q7"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6 A7:B7">
+    <cfRule type="expression" dxfId="17" priority="1">
+      <formula>AND($B$5&lt;&gt;"",$B$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6 D7:E7">
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>AND($E$5&lt;&gt;"",$E$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6 G7:H7">
+    <cfRule type="expression" dxfId="15" priority="3">
+      <formula>AND($H$5&lt;&gt;"",$H$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6 J7:K7">
+    <cfRule type="expression" dxfId="14" priority="4">
+      <formula>AND($K$5&lt;&gt;"",$K$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N6 M7:N7">
+    <cfRule type="expression" dxfId="13" priority="5">
+      <formula>AND($N$5&lt;&gt;"",$N$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q6 P7:Q7">
+    <cfRule type="expression" dxfId="12" priority="6">
+      <formula>AND($Q$5&lt;&gt;"",$Q$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T6 S7:T7">
+    <cfRule type="expression" dxfId="11" priority="7">
+      <formula>AND($T$5&lt;&gt;"",$T$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W6 V7:W7">
+    <cfRule type="expression" dxfId="10" priority="8">
+      <formula>AND($W$5&lt;&gt;"",$W$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z6 Y7:Z7">
+    <cfRule type="expression" dxfId="9" priority="9">
+      <formula>AND($Z$5&lt;&gt;"",$Z$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC6 AB7:AC7">
+    <cfRule type="expression" dxfId="8" priority="10">
+      <formula>AND($AC$5&lt;&gt;"",$AC$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF6 AE7:AF7">
+    <cfRule type="expression" dxfId="7" priority="11">
+      <formula>AND($AF$5&lt;&gt;"",$AF$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI6 AH7:AI7">
+    <cfRule type="expression" dxfId="6" priority="12">
+      <formula>AND($AI$5&lt;&gt;"",$AI$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL6 AK7:AL7">
+    <cfRule type="expression" dxfId="5" priority="13">
+      <formula>AND($AL$5&lt;&gt;"",$AL$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO6 AN7:AO7">
+    <cfRule type="expression" dxfId="4" priority="14">
+      <formula>AND($AO$5&lt;&gt;"",$AO$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AR6 AQ7:AR7">
+    <cfRule type="expression" dxfId="3" priority="15">
+      <formula>AND($AR$5&lt;&gt;"",$AR$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5 E5 H5 K5 N5 Q5 T5 W5 Z5 AC5 AF5 AI5 AL5 AO5 AR5" xr:uid="{00000000-0002-0000-0400-000000000000}">
+      <formula1>"material,ssr reduce,ssr hold,ssr elastic,refine"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17815,17 +18315,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3:E42">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>OR($D3="Intercept", $D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:G42">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>OR($D3="Depth",$D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H42">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>OR($D3="Depth",$D3="Intercept")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18000,7 +18500,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="B2:X22"/>
+  <dimension ref="B2:X23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -18050,80 +18550,92 @@
       <c r="X2" s="62"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="39"/>
+      <c r="F3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="G3" s="58"/>
+      <c r="H3" s="39"/>
+      <c r="J3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="K3" s="58"/>
+      <c r="L3" s="39"/>
+      <c r="N3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="O3" s="58"/>
+      <c r="P3" s="39"/>
+      <c r="R3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="S3" s="58"/>
+      <c r="T3" s="39"/>
+      <c r="V3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="W3" s="58"/>
+      <c r="X3" s="39"/>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="3"/>
@@ -18485,15 +18997,46 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="V2:X2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="F2:H2"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="R3:S3"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 H3 L3 P3 T3 X3" xr:uid="{00000000-0002-0000-0800-000000000000}">
+      <formula1>"normal,vertical"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/verification/files/rocscience_gw/gw019.xlsx
+++ b/docs/verification/files/rocscience_gw/gw019.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C0E255-0472-174F-97B1-AC3DD61E05E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523500CF-89B8-4644-B955-31C74218CF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18260" yWindow="3440" windowWidth="44060" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="4320" windowWidth="46940" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="318">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -875,9 +875,6 @@
   </si>
   <si>
     <t>I</t>
-  </si>
-  <si>
-    <t>Fixity</t>
   </si>
   <si>
     <t>P</t>
@@ -1116,6 +1113,27 @@
   </si>
   <si>
     <t>yr</t>
+  </si>
+  <si>
+    <t>Adhesion</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>1D element size:</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>Tip</t>
+  </si>
+  <si>
+    <t>Pinned</t>
+  </si>
+  <si>
+    <t>Unrotated</t>
   </si>
 </sst>
 </file>
@@ -1886,16 +1904,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>217714</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>54430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>199571</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>9071</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>90714</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1910,8 +1928,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14804571" y="254001"/>
-          <a:ext cx="3610429" cy="3746499"/>
+          <a:off x="16455571" y="254001"/>
+          <a:ext cx="3855358" cy="4027713"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2035,6 +2053,31 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Adhesion</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = soii-reinforcement interface adhesion (blank</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = use Lp)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>Delta</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = soil-reinforcement interface friction angle (blank = use Lp)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Tend1, Tend2 </a:t>
           </a:r>
           <a:r>
@@ -2081,6 +2124,10 @@
             <a:rPr lang="en-US" sz="1100" b="0"/>
             <a:t> = cross-sectional area of reinforcement (FEM only)</a:t>
           </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2093,16 +2140,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>308429</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>290286</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:rowOff>126999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>571501</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>145143</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>553358</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2117,8 +2164,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13398500" y="190499"/>
-          <a:ext cx="3156858" cy="2349501"/>
+          <a:off x="14205857" y="126999"/>
+          <a:ext cx="3156858" cy="2521858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2423,7 +2470,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Fixity</a:t>
+            <a:t>Head</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
@@ -2435,8 +2482,54 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> = Pile head status (fixed or free)</a:t>
+            <a:t> = Pile head fixity status</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tip</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile tip fixity status</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -2788,7 +2881,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="30">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -2968,7 +3061,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C20" s="14" t="s">
-        <v>45</v>
+        <v>313</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>46</v>
@@ -2980,7 +3073,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C21" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>49</v>
@@ -2992,28 +3085,34 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="1"/>
+        <v>48</v>
+      </c>
       <c r="F22" s="1"/>
+      <c r="D22"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
       <c r="C23" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="1"/>
-      <c r="C24" s="14" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D24"/>
+      <c r="D25"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="s">
@@ -3057,7 +3156,7 @@
     </row>
     <row r="58" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D58" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
@@ -3155,7 +3254,7 @@
     <mergeCell ref="B7:D7"/>
   </mergeCells>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"rollers,fixed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -3173,10 +3272,10 @@
     <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>$D$75:$D$79</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"auto,manual"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D25" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"circular,non-circular"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3186,18 +3285,18 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A2:AB25"/>
+  <dimension ref="A2:AD25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="6" width="10.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" customWidth="1"/>
-    <col min="10" max="12" width="10.83203125" style="1" customWidth="1"/>
-    <col min="16" max="18" width="10.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="4.33203125" customWidth="1"/>
+    <col min="10" max="14" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="20" width="10.83203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>194</v>
       </c>
@@ -3235,34 +3334,40 @@
         <v>252</v>
       </c>
       <c r="M2" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="O2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="R2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="Q2" s="28" t="s">
+      <c r="S2" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="R2" s="28" t="s">
+      <c r="T2" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>258</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>259</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3273,11 +3378,11 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="str">
-        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,2,0),""))</f>
+        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,3,0),""))</f>
+        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J3" s="3"/>
@@ -3289,17 +3394,19 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
-      <c r="Z3" t="s">
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="AB3" t="s">
         <v>261</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AC3" t="s">
         <v>262</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AD3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -3326,11 +3433,13 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
-      <c r="Z4" t="s">
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="AB4" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -3357,11 +3466,13 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-      <c r="Z5" t="s">
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="AB5" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -3388,8 +3499,10 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -3416,8 +3529,10 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -3444,17 +3559,19 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-      <c r="Z8" t="s">
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="AB8" t="s">
         <v>258</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AC8" t="s">
         <v>259</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AD8" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -3481,17 +3598,19 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="Z9" t="s">
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="AB9" t="s">
         <v>261</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AC9" t="s">
         <v>262</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AD9" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -3518,17 +3637,19 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="Z10" t="s">
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="AB10" t="s">
         <v>264</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="AC10" t="s">
         <v>262</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AD10" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -3555,17 +3676,19 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="Z11" t="s">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="AB11" t="s">
         <v>265</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AC11" t="s">
         <v>262</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AD11" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -3592,8 +3715,10 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -3620,8 +3745,10 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -3648,8 +3775,10 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -3676,8 +3805,10 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -3704,8 +3835,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -3732,8 +3865,10 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -3760,8 +3895,10 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -3788,8 +3925,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -3816,8 +3955,10 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -3844,8 +3985,10 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -3872,39 +4015,41 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="T23" s="42"/>
-      <c r="U23" t="s">
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V23" s="42"/>
+      <c r="W23" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="9" t="s">
+      <c r="V24" s="26"/>
+      <c r="W24" s="9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="9" t="s">
+      <c r="V25" s="29"/>
+      <c r="W25" s="9" t="s">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G22" xr:uid="{00000000-0002-0000-0900-000000000000}">
-      <formula1>$Z$2:$Z$5</formula1>
+      <formula1>$AB$2:$AB$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H22" xr:uid="{00000000-0002-0000-0900-000001000000}">
-      <formula1>$AA$2:$AA$3</formula1>
+      <formula1>$AC$2:$AC$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I22" xr:uid="{00000000-0002-0000-0900-000002000000}">
-      <formula1>$AB$2:$AB$3</formula1>
+      <formula1>$AD$2:$AD$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3914,18 +4059,18 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A2:Z17"/>
+  <dimension ref="A2:AA17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
     <col min="3" max="7" width="10.83203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" customWidth="1"/>
-    <col min="9" max="16" width="10.83203125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="5.5" customWidth="1"/>
+    <col min="9" max="17" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>194</v>
       </c>
@@ -3972,16 +4117,19 @@
         <v>257</v>
       </c>
       <c r="P2" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="Y2" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>315</v>
+      </c>
+      <c r="Z2" t="s">
         <v>222</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -4000,14 +4148,15 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
-      <c r="Y3" t="s">
-        <v>226</v>
-      </c>
+      <c r="Q3" s="3"/>
       <c r="Z3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AA3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -4026,8 +4175,12 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q4" s="3"/>
+      <c r="Z4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -4046,8 +4199,12 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q5" s="3"/>
+      <c r="Z5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -4066,8 +4223,9 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -4086,8 +4244,9 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -4106,8 +4265,9 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -4126,8 +4286,9 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -4146,8 +4307,9 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -4166,8 +4328,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -4186,36 +4349,37 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R15" s="42"/>
-      <c r="S15" t="s">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S15" s="42"/>
+      <c r="T15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R16" s="26"/>
-      <c r="S16" s="9" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S16" s="26"/>
+      <c r="T16" s="9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="18:19" x14ac:dyDescent="0.2">
-      <c r="R17" s="29"/>
-      <c r="S17" s="9" t="s">
+    <row r="17" spans="19:20" x14ac:dyDescent="0.2">
+      <c r="S17" s="29"/>
+      <c r="T17" s="9" t="s">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
-      <formula1>$Y$2:$Y$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
+      <formula1>$AA$2:$AA$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
-      <formula1>$Z$2:$Z$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>$Z$2:$Z$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4247,10 +4411,10 @@
         <v>167</v>
       </c>
       <c r="E2" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>273</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -4473,27 +4637,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="59" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="59" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="59" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="59" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4519,19 +4683,19 @@
         <v>5.0</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
@@ -4572,10 +4736,10 @@
         <v>167</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="U4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4600,10 +4764,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="U5" t="s">
         <v>284</v>
-      </c>
-      <c r="U5" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4628,7 +4792,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -4917,27 +5081,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="60" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="60" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="60" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="60" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4945,27 +5109,27 @@
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F3" s="35"/>
       <c r="H3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I3" s="35"/>
       <c r="K3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
@@ -5006,10 +5170,10 @@
         <v>167</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="U4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -5026,10 +5190,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="U5" t="s">
         <v>284</v>
-      </c>
-      <c r="U5" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -5338,16 +5502,16 @@
         </is>
       </c>
       <c r="D2" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="E2" s="50" t="s">
         <v>295</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="F2" s="50" t="s">
         <v>296</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="G2" s="50" t="s">
         <v>297</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -5362,7 +5526,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J3" s="3">
         <v>11351.34</v>
@@ -5390,7 +5554,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -5412,7 +5576,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -5424,7 +5588,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -5436,7 +5600,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -6461,7 +6625,7 @@
         <v>113</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E10" s="44" t="s">
         <v>114</v>
@@ -6530,22 +6694,22 @@
         <v>134</v>
       </c>
       <c r="AA10" s="46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AB10" s="46" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AC10" s="47" t="s">
         <v>135</v>
       </c>
       <c r="AD10" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="AE10" s="46" t="s">
         <v>307</v>
       </c>
-      <c r="AE10" s="46" t="s">
+      <c r="AF10" s="47" t="s">
         <v>308</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>309</v>
       </c>
       <c r="AG10" s="23" t="s">
         <v>136</v>
@@ -10899,6 +11063,7 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="S4:T4"/>
     <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH4:AI4"/>
@@ -10928,7 +11093,6 @@
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="S4:T4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">
@@ -11269,7 +11433,7 @@
         <v>9.5</v>
       </c>
       <c r="C3" s="3">
-        <v>20.0</v>
+        <v>10.6257142857</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -11277,7 +11441,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -11671,7 +11835,7 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
@@ -12220,7 +12384,7 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
